--- a/Design/Excel/ET/Datas/Product/RestaurantChapterConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/RestaurantChapterConfig.xlsx
@@ -939,157 +939,163 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <x:cols>
-    <x:col min="1" max="1" width="21.125" style="2" customWidth="1"/>
-    <x:col min="2" max="2" width="12.75" style="2" customWidth="1"/>
-    <x:col min="3" max="4" width="12.625" style="2" customWidth="1"/>
-    <x:col min="5" max="5" width="15.125" style="2" customWidth="1"/>
-    <x:col min="6" max="6" width="9.625" style="2" customWidth="1"/>
-    <x:col min="7" max="7" width="28.75" style="2" customWidth="1"/>
-    <x:col min="8" max="9" width="11.75" style="2" customWidth="1"/>
-    <x:col min="10" max="10" width="6.75" style="2" customWidth="1"/>
-    <x:col min="11" max="16384" width="9" style="2" customWidth="0"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" t="str">
-        <x:v>##var</x:v>
-      </x:c>
-      <x:c r="B1" t="str">
-        <x:v>Id</x:v>
-      </x:c>
-      <x:c r="C1" t="str">
-        <x:v>Name</x:v>
-      </x:c>
-      <x:c r="D1" t="str">
-        <x:v>MenuVariant</x:v>
-      </x:c>
-      <x:c r="E1" t="str">
-        <x:v>SoloChapterId</x:v>
-      </x:c>
-      <x:c r="F1" t="str">
-        <x:v>CooperativeChapterId</x:v>
-      </x:c>
-      <x:c r="G1" t="str">
-        <x:v>SoloFirstLevelId</x:v>
-      </x:c>
-      <x:c r="H1" t="str">
-        <x:v>CooperativeFirstLevelId</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="str">
-        <x:v>##type</x:v>
-      </x:c>
-      <x:c r="B2" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="C2" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="D2" t="str">
-        <x:v>ProductMenuVariant</x:v>
-      </x:c>
-      <x:c r="E2" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="F2" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="G2" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="H2" t="str">
-        <x:v>int</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" t="str">
-        <x:v>##</x:v>
-      </x:c>
-      <x:c r="B3" t="str">
-        <x:v>内容章身份</x:v>
-      </x:c>
-      <x:c r="C3" t="str">
-        <x:v>名称</x:v>
-      </x:c>
-      <x:c r="D3" t="str">
-        <x:v>资源组合</x:v>
-      </x:c>
-      <x:c r="E3" t="str">
-        <x:v>Solo关链身份</x:v>
-      </x:c>
-      <x:c r="F3" t="str">
-        <x:v>合作关链身份</x:v>
-      </x:c>
-      <x:c r="G3" t="str">
-        <x:v>Solo首关</x:v>
-      </x:c>
-      <x:c r="H3" t="str">
-        <x:v>合作首关</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" t="str"/>
-      <x:c r="B4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" t="str">
-        <x:v>家常开张</x:v>
-      </x:c>
-      <x:c r="D4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E4" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F4" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G4" t="n">
-        <x:v>1101</x:v>
-      </x:c>
-      <x:c r="H4" t="n">
-        <x:v>2101</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" t="str"/>
-      <x:c r="B5" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" t="str">
-        <x:v>进阶小馆</x:v>
-      </x:c>
-      <x:c r="D5" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="E5" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F5" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G5" t="n">
-        <x:v>1501</x:v>
-      </x:c>
-      <x:c r="H5" t="n">
-        <x:v>2501</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="str"/>
-      <x:c r="B6" t="str"/>
-      <x:c r="C6" t="str"/>
-      <x:c r="D6" t="str"/>
-      <x:c r="E6" t="str"/>
-      <x:c r="F6" t="str"/>
-      <x:c r="G6" t="str"/>
-      <x:c r="H6" t="str"/>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
+    <col min="3" max="4" width="12.625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="28.75" style="2" customWidth="1"/>
+    <col min="8" max="9" width="11.75" style="2" customWidth="1"/>
+    <col min="10" max="10" width="6.75" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2" customWidth="0"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>##var</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Id</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Name</v>
+      </c>
+      <c r="D1" t="str">
+        <v>MenuVariant</v>
+      </c>
+      <c r="E1" t="str">
+        <v>SoloChapterId</v>
+      </c>
+      <c r="F1" t="str">
+        <v>CooperativeChapterId</v>
+      </c>
+      <c r="G1" t="str">
+        <v>SoloFirstLevelId</v>
+      </c>
+      <c r="H1" t="str">
+        <v>CooperativeFirstLevelId</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>##type</v>
+      </c>
+      <c r="B2" t="str">
+        <v>int</v>
+      </c>
+      <c r="C2" t="str">
+        <v>string</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ProductMenuVariant</t>
+        </is>
+      </c>
+      <c r="E2" t="str">
+        <v>int</v>
+      </c>
+      <c r="F2" t="str">
+        <v>int</v>
+      </c>
+      <c r="G2" t="str">
+        <v>int</v>
+      </c>
+      <c r="H2" t="str">
+        <v>int</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>##</v>
+      </c>
+      <c r="B3" t="str">
+        <v>内容章身份</v>
+      </c>
+      <c r="C3" t="str">
+        <v>名称</v>
+      </c>
+      <c r="D3" t="str">
+        <v>资源组合</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Solo关链身份</v>
+      </c>
+      <c r="F3" t="str">
+        <v>合作关链身份</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Solo首关</v>
+      </c>
+      <c r="H3" t="str">
+        <v>合作首关</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str"/>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="str">
+        <v>家常开张</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F4" t="n">
+        <v>21</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1101</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2101</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str"/>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="str">
+        <v>进阶小馆</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>22</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1501</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str"/>
+      <c r="B6" t="str"/>
+      <c r="C6" t="str"/>
+      <c r="D6" t="str"/>
+      <c r="E6" t="str"/>
+      <c r="F6" t="str"/>
+      <c r="G6" t="str"/>
+      <c r="H6" t="str"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>